--- a/docs/BPML-Konzept.xlsx
+++ b/docs/BPML-Konzept.xlsx
@@ -111,13 +111,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00C0392B"/>
+      <color rgb="00B8860B"/>
       <sz val="9.5"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B8860B"/>
+      <color rgb="00C0392B"/>
       <sz val="9.5"/>
     </font>
     <font>
@@ -253,13 +253,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -834,10 +834,10 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="44" customHeight="1">
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>✓ Formatierter Excel-Export (ExcelJS) mit 6 Blättern: Deckblatt, BPML (gruppiert), Länder-Matrix, Länderspezifika, Abschlusskalender, AFC-Task-Liste.</t>
+          <t>✓ Formatierter 6-Blatt-Excel-Export · verlustfreier Round-Trip (Export wieder einladbar) · Undo/Redo · Bearbeiter/Urheber im Protokoll · Abweichungsgrund im Editor (inkl. Fix: Länder-Scope wurde bisher aus dem Editor nicht gespeichert).</t>
         </is>
       </c>
     </row>
@@ -1282,9 +1282,9 @@
           <t>Hoch</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>✗ fehlt</t>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>✓ vorhanden</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
           <t>im Workshop flexibel sein</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t>Niedrig</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>◐ teilweise</t>
         </is>
@@ -1488,9 +1488,9 @@
           <t>Mittel</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>◐ teilweise</t>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>✓ vorhanden</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
           <t>die Kontrolldichte bewerten</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Niedrig</t>
         </is>
@@ -1772,7 +1772,7 @@
           <t>Hoch</t>
         </is>
       </c>
-      <c r="F28" s="19" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>◐ teilweise</t>
         </is>
@@ -1875,7 +1875,7 @@
           <t>Hoch</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>✗ fehlt</t>
         </is>
@@ -1939,7 +1939,7 @@
           <t>Mittel</t>
         </is>
       </c>
-      <c r="F34" s="19" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>◐ teilweise</t>
         </is>
@@ -2160,32 +2160,57 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Offen / nächste Schritte</t>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Round-Trip: Export wieder einladbar</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Export war reine Ausgabe</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Voller Stand als verstecktes _bpml-Blatt eingebettet; „⬆ Excel“ lädt ihn verlustfrei</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>✓ umgesetzt</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>G-04</t>
+          <t>G-05</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Live-Mehrbenutzer-Zusammenarbeit</t>
+          <t>Undo / Redo</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Nur Export/Import + Git, kein Realtime</t>
+          <t>Keins; Löschen endgültig</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Gemeinsames Backend / gleichzeitiges Bearbeiten</t>
+          <t>Rückgängig/Wiederherstellen (Toolbar + Strg+Z/Umschalt+Z), max. 60 Schritte</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -2193,73 +2218,48 @@
           <t>Hoch</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>✓ umgesetzt</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>G-05</t>
+          <t>G-06</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Undo / Redo</t>
+          <t>Abweichungsgrund im Editor</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Keins; Löschen endgültig (mit Bestätigung)</t>
+          <t>reason wurde im Editor gar nicht gespeichert (Länder-Scope-Bug)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Rückgängig/Wiederherstellen über mehrere Schritte</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>offen</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>G-06</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Kunden-Excel-Mapping</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Generisches Alias-Mapping</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>An reales Kundenlayout angepasst (Phase-0)</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>offen</t>
+          <t>Scope, Abweichung &amp; Begründung je Land im Editor pflegbar; Bug behoben</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Mittel</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>✓ umgesetzt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Offen / nächste Schritte</t>
         </is>
       </c>
     </row>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Audit-Trail mit Urheber</t>
+          <t>Audit-Trail exportierbar</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Änderungsprotokoll ohne „wer“</t>
+          <t>Urheber wird jetzt erfasst, aber nur im Protokoll</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Nutzer je Änderung + exportierbarer Prüfnachweis</t>
+          <t>Prüfnachweis exportierbar; echte Authentifizierung</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
@@ -2289,9 +2289,9 @@
           <t>Mittel</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>offen</t>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>◐ teilweise umgesetzt</t>
         </is>
       </c>
     </row>
@@ -2303,27 +2303,27 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Landesgefilterte Sicht / Teil-Export</t>
+          <t>Live-Mehrbenutzer-Zusammenarbeit</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Nur Filter im UI</t>
+          <t>Nur Export/Import + Git, kein Realtime</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Pro Land eine eigene Sicht/Datei</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>Mittel</t>
+          <t>Gemeinsames Backend / gleichzeitiges Bearbeiten</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>◐ teilweise umgesetzt</t>
+          <t>offen</t>
         </is>
       </c>
     </row>
@@ -2335,25 +2335,25 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Abweichungsgrund in der UI</t>
+          <t>Kunden-Excel-Mapping</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>reason im Modell, UI nur teilweise</t>
+          <t>Generisches Alias-Mapping</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Begründung überall komfortabel erfassbar</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>Mittel</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
+          <t>An reales Kundenlayout angepasst (Phase-0, braucht echte Datei)</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Hoch</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
@@ -2380,12 +2380,12 @@
           <t>Umsortieren auch per Touch</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t>Niedrig</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
@@ -2412,12 +2412,12 @@
           <t>Sauberes Druck-/PDF-Layout je Ansicht</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t>Niedrig</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
@@ -2444,12 +2444,12 @@
           <t>Robust bei sehr großen Listen (z. B. IndexedDB)</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>Niedrig</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
@@ -2476,12 +2476,12 @@
           <t>Auf main umstellen, sobald gemergt</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>Niedrig</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>offen</t>
         </is>
@@ -2489,8 +2489,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
